--- a/data/trans_orig/IQ23_R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ23_R2-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>603</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5409</t>
+          <t>5522</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4254</t>
+          <t>4750</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1692</t>
+          <t>1697</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7290</t>
+          <t>7371</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19238</t>
+          <t>18378</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34083</t>
+          <t>32533</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24176</t>
+          <t>23386</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39987</t>
+          <t>39453</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>46908</t>
+          <t>47788</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>69416</t>
+          <t>69282</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,02%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>100268</t>
+          <t>101301</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>116001</t>
+          <t>115693</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>74,09%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>110604</t>
+          <t>110858</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>126360</t>
+          <t>127063</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>214210</t>
+          <t>215379</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>237780</t>
+          <t>237591</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,37%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1942</t>
+          <t>2420</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9518</t>
+          <t>9512</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9643</t>
+          <t>9367</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5679</t>
+          <t>5730</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16063</t>
+          <t>15233</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31665</t>
+          <t>30970</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>49168</t>
+          <t>48353</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33415</t>
+          <t>33338</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>51593</t>
+          <t>51672</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>70127</t>
+          <t>69117</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>94082</t>
+          <t>94547</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,29%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>140382</t>
+          <t>140867</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>158605</t>
+          <t>158328</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>155016</t>
+          <t>154669</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>173812</t>
+          <t>173590</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>73,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>301099</t>
+          <t>301144</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>326880</t>
+          <t>328619</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,95%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2158</t>
+          <t>2108</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8194</t>
+          <t>8323</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7131</t>
+          <t>7024</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4380</t>
+          <t>4240</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>13053</t>
+          <t>12728</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33333</t>
+          <t>33928</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50519</t>
+          <t>49941</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31186</t>
+          <t>31296</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47495</t>
+          <t>47842</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>69184</t>
+          <t>68577</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>92801</t>
+          <t>92695</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,4%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>82170</t>
+          <t>82304</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>99193</t>
+          <t>98946</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>98354</t>
+          <t>98077</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>115384</t>
+          <t>115510</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>184988</t>
+          <t>185304</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>209370</t>
+          <t>210021</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>73,41%</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9692</t>
+          <t>9008</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3472</t>
+          <t>3649</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12004</t>
+          <t>12515</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>46461</t>
+          <t>46396</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>68081</t>
+          <t>68903</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>50874</t>
+          <t>51324</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>71789</t>
+          <t>71566</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>102443</t>
+          <t>103755</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>133945</t>
+          <t>132967</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,11%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>136057</t>
+          <t>135697</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>158934</t>
+          <t>158117</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>130250</t>
+          <t>130431</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>151546</t>
+          <t>151904</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>273582</t>
+          <t>274114</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>304756</t>
+          <t>303306</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>73,24%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9416</t>
+          <t>8796</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20927</t>
+          <t>20996</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9022</t>
+          <t>9016</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>21127</t>
+          <t>21544</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>20730</t>
+          <t>20883</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>37295</t>
+          <t>38157</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>146738</t>
+          <t>146346</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>182586</t>
+          <t>182479</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>154862</t>
+          <t>155237</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>191573</t>
+          <t>191514</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>312048</t>
+          <t>310892</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>362266</t>
+          <t>362724</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,01%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>477467</t>
+          <t>478826</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>514381</t>
+          <t>515681</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>511759</t>
+          <t>513998</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>550048</t>
+          <t>550329</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>71,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1003068</t>
+          <t>1002908</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1055854</t>
+          <t>1055340</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,67%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>655</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6907</t>
+          <t>6231</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>1910</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9976</t>
+          <t>10691</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>3128</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12944</t>
+          <t>12755</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22139</t>
+          <t>21865</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39313</t>
+          <t>38259</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30106</t>
+          <t>30079</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49125</t>
+          <t>48215</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>57214</t>
+          <t>57906</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>81413</t>
+          <t>81121</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,65%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>98066</t>
+          <t>98760</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>114949</t>
+          <t>115276</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>100081</t>
+          <t>100925</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>119445</t>
+          <t>119556</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>205414</t>
+          <t>205021</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>230137</t>
+          <t>228928</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,03%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3614</t>
+          <t>3683</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12054</t>
+          <t>12281</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4617</t>
+          <t>4638</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13873</t>
+          <t>14941</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9845</t>
+          <t>9931</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>22848</t>
+          <t>22216</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>39844</t>
+          <t>39987</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>58528</t>
+          <t>58543</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44804</t>
+          <t>45985</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>65614</t>
+          <t>66727</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>89714</t>
+          <t>89817</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>120706</t>
+          <t>118283</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,54%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>140940</t>
+          <t>140100</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>160478</t>
+          <t>159911</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>148355</t>
+          <t>147539</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>170170</t>
+          <t>169409</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>294006</t>
+          <t>295464</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>324979</t>
+          <t>324177</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>68,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>75,47%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1840</t>
+          <t>1602</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9124</t>
+          <t>8944</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2484</t>
+          <t>2549</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9601</t>
+          <t>9764</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5033</t>
+          <t>5777</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15191</t>
+          <t>15647</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39141</t>
+          <t>38437</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56781</t>
+          <t>57051</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32428</t>
+          <t>32586</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49926</t>
+          <t>50497</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>76925</t>
+          <t>77087</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>103510</t>
+          <t>103127</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,1%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>93102</t>
+          <t>94535</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>111779</t>
+          <t>112535</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>72,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>110847</t>
+          <t>110383</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>128872</t>
+          <t>128908</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>208620</t>
+          <t>208748</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>235496</t>
+          <t>234647</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>64,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,3%</t>
+          <t>73,03%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1484</t>
+          <t>1481</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8988</t>
+          <t>8801</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7425</t>
+          <t>7335</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>3573</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12947</t>
+          <t>12965</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>44095</t>
+          <t>45672</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>66412</t>
+          <t>66910</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>46144</t>
+          <t>46546</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>68093</t>
+          <t>67813</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>97626</t>
+          <t>97594</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>129014</t>
+          <t>127564</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,52%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>138767</t>
+          <t>138212</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>161735</t>
+          <t>161041</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>136336</t>
+          <t>136521</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>158768</t>
+          <t>158336</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>282248</t>
+          <t>282231</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>313317</t>
+          <t>312740</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>74,83%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11459</t>
+          <t>11417</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>25823</t>
+          <t>24964</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15772</t>
+          <t>15187</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>29831</t>
+          <t>31094</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>30103</t>
+          <t>29396</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>51410</t>
+          <t>50495</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>162579</t>
+          <t>161945</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>200260</t>
+          <t>200562</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>172062</t>
+          <t>173928</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>212520</t>
+          <t>214090</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>343734</t>
+          <t>345473</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>398703</t>
+          <t>402882</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,56%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>490168</t>
+          <t>491483</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>529356</t>
+          <t>531483</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>69,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>517703</t>
+          <t>516931</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>559539</t>
+          <t>557348</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1022475</t>
+          <t>1019954</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1079630</t>
+          <t>1078025</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>73,73%</t>
         </is>
       </c>
     </row>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8281</t>
+          <t>8350</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>689</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6749</t>
+          <t>6756</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,7 +5807,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3087</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11938</t>
+          <t>12045</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16618</t>
+          <t>16402</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31507</t>
+          <t>30894</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32234</t>
+          <t>31095</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50571</t>
+          <t>49609</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>51910</t>
+          <t>52818</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>75294</t>
+          <t>76361</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>27,1%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>98767</t>
+          <t>98601</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>114100</t>
+          <t>114221</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>95360</t>
+          <t>96250</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>113484</t>
+          <t>114155</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>199603</t>
+          <t>198590</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>223634</t>
+          <t>222992</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,14%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>1648</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7697</t>
+          <t>7837</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>1253</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7151</t>
+          <t>6995</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3787</t>
+          <t>3926</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11918</t>
+          <t>12405</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>59257</t>
+          <t>58117</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>80975</t>
+          <t>80229</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>65220</t>
+          <t>64455</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>87872</t>
+          <t>87431</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>130546</t>
+          <t>129723</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>161453</t>
+          <t>162041</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,69%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>122487</t>
+          <t>121697</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>143366</t>
+          <t>143436</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>133166</t>
+          <t>132883</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>155742</t>
+          <t>155643</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>260897</t>
+          <t>260957</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>292574</t>
+          <t>293822</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>60,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>68,35%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2246</t>
+          <t>1827</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8184</t>
+          <t>8601</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5605</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3456</t>
+          <t>3472</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11627</t>
+          <t>11823</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6759,7 +6759,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37429</t>
+          <t>37657</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54633</t>
+          <t>55035</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44640</t>
+          <t>44256</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>64836</t>
+          <t>64290</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>86495</t>
+          <t>86332</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>111719</t>
+          <t>112879</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,52%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>94199</t>
+          <t>93412</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>112177</t>
+          <t>110926</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>97893</t>
+          <t>98594</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>118113</t>
+          <t>118485</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>59,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>199020</t>
+          <t>197184</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>224784</t>
+          <t>225080</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>70,83%</t>
         </is>
       </c>
     </row>
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7774</t>
+          <t>7823</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8207</t>
+          <t>7546</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7215,7 +7215,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>57475</t>
+          <t>57145</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>80448</t>
+          <t>79760</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>51315</t>
+          <t>52084</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>73332</t>
+          <t>75107</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>114823</t>
+          <t>115474</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>147517</t>
+          <t>146751</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>35,96%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>125559</t>
+          <t>126247</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>148532</t>
+          <t>148862</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>61,28%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>124876</t>
+          <t>123503</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>147211</t>
+          <t>146603</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>257479</t>
+          <t>258075</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>291108</t>
+          <t>289525</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>63,24%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>70,95%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7642</t>
+          <t>7578</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18865</t>
+          <t>19089</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7175</t>
+          <t>6835</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18438</t>
+          <t>17898</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>16830</t>
+          <t>16195</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>31855</t>
+          <t>31552</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>186700</t>
+          <t>188877</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>225389</t>
+          <t>226691</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>212308</t>
+          <t>212559</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>253233</t>
+          <t>254974</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>414722</t>
+          <t>412495</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>472665</t>
+          <t>468156</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,57%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>461446</t>
+          <t>458336</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>500446</t>
+          <t>497620</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>474082</t>
+          <t>472693</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>515200</t>
+          <t>515355</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>939878</t>
+          <t>945678</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>999255</t>
+          <t>1002204</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,72%</t>
         </is>
       </c>
     </row>
@@ -8274,7 +8274,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3427</t>
+          <t>3210</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3666</t>
+          <t>2691</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8359,7 +8359,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25569</t>
+          <t>25052</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39200</t>
+          <t>39189</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28735</t>
+          <t>28602</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50584</t>
+          <t>51122</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>58364</t>
+          <t>58165</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>84216</t>
+          <t>84663</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,33%</t>
         </is>
       </c>
     </row>
@@ -8495,12 +8495,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>75257</t>
+          <t>75336</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>89449</t>
+          <t>89582</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8510,12 +8510,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>88227</t>
+          <t>87689</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>110076</t>
+          <t>110209</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>168640</t>
+          <t>168474</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>195003</t>
+          <t>195201</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>66,33%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,85%</t>
         </is>
       </c>
     </row>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4614</t>
+          <t>4627</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8745,7 +8745,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>940</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12452</t>
+          <t>12272</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1761</t>
+          <t>1717</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12947</t>
+          <t>14278</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -8838,12 +8838,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>39922</t>
+          <t>40130</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>60293</t>
+          <t>60502</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>56547</t>
+          <t>56846</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>81069</t>
+          <t>81442</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>101560</t>
+          <t>102866</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>134638</t>
+          <t>135739</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,47%</t>
         </is>
       </c>
     </row>
@@ -8951,12 +8951,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>129021</t>
+          <t>128491</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>149491</t>
+          <t>149487</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>168742</t>
+          <t>168907</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>194046</t>
+          <t>193958</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9001,12 +9001,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>66,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>304337</t>
+          <t>305051</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>338525</t>
+          <t>337754</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>75,81%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2576</t>
+          <t>2456</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12392</t>
+          <t>11663</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2995</t>
+          <t>3121</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3589</t>
+          <t>3253</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>13484</t>
+          <t>13447</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -9294,12 +9294,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25389</t>
+          <t>25272</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54890</t>
+          <t>54542</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48595</t>
+          <t>49276</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>75340</t>
+          <t>75452</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>78972</t>
+          <t>78638</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>122729</t>
+          <t>122459</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,86%</t>
         </is>
       </c>
     </row>
@@ -9407,12 +9407,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>126145</t>
+          <t>125472</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>157739</t>
+          <t>158208</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>108534</t>
+          <t>108542</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>135289</t>
+          <t>134291</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>72,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>242609</t>
+          <t>243568</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>288096</t>
+          <t>289660</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>77,72%</t>
         </is>
       </c>
     </row>
@@ -9642,7 +9642,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3579</t>
+          <t>2977</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>825</t>
+          <t>831</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>7318</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>865</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8646</t>
+          <t>8222</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9727,7 +9727,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>48988</t>
+          <t>48736</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>69707</t>
+          <t>70427</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>41602</t>
+          <t>42700</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>63467</t>
+          <t>64618</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>95468</t>
+          <t>96790</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>126592</t>
+          <t>127635</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>36,74%</t>
         </is>
       </c>
     </row>
@@ -9863,12 +9863,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>95883</t>
+          <t>95388</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>116596</t>
+          <t>116921</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>114529</t>
+          <t>114470</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>137207</t>
+          <t>135842</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>216535</t>
+          <t>217619</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>247676</t>
+          <t>247367</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>71,21%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4663</t>
+          <t>4474</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15615</t>
+          <t>14902</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3610</t>
+          <t>3613</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>17103</t>
+          <t>18565</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10260</t>
+          <t>10404</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>26964</t>
+          <t>27234</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -10206,12 +10206,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>154090</t>
+          <t>156452</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>204120</t>
+          <t>203213</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>199124</t>
+          <t>198071</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>247200</t>
+          <t>247350</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>368954</t>
+          <t>369573</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>440360</t>
+          <t>434975</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,64%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>447035</t>
+          <t>447861</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>496594</t>
+          <t>495758</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>503401</t>
+          <t>504217</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>552053</t>
+          <t>554632</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>963471</t>
+          <t>967512</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1034488</t>
+          <t>1032773</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>72,75%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ23_R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ23_R2-Habitat-trans_orig.xlsx
@@ -726,213 +726,213 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>1284</v>
+        <v>31491</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0</v>
+        <v>23937</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>4471</v>
+        <v>39560</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.008464803435959931</v>
+        <v>0.2075631965541583</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0</v>
+        <v>0.1577717777914656</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.02946808221361957</v>
+        <v>0.2607451901246275</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>2378</v>
+        <v>25688</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>616</v>
+        <v>19059</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>5926</v>
+        <v>33067</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.01738812672713651</v>
+        <v>0.1878657239173462</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.004504064889290805</v>
+        <v>0.1393873306032985</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.043340154559706</v>
+        <v>0.2418307744403922</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>6</v>
+        <v>86</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>3662</v>
+        <v>57179</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>1716</v>
+        <v>46609</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>7389</v>
+        <v>68282</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.01269468013738443</v>
+        <v>0.1982261056672033</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.00594815053882774</v>
+        <v>0.161580544093606</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.0256156654943652</v>
+        <v>0.2367177423352348</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>47</v>
+        <v>175</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>31491</v>
+        <v>118944</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>23937</v>
+        <v>110913</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>39560</v>
+        <v>126611</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.2075631965541583</v>
+        <v>0.7839720000098818</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.1577717777914656</v>
+        <v>0.7310392440055646</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.2607451901246275</v>
+        <v>0.8345064092620026</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>39</v>
+        <v>157</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>25688</v>
+        <v>108670</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>19059</v>
+        <v>100848</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>33067</v>
+        <v>115322</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.1878657239173462</v>
+        <v>0.7947461493555172</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.1393873306032985</v>
+        <v>0.7375426385262301</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.2418307744403922</v>
+        <v>0.8433970866873363</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>86</v>
+        <v>332</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>57179</v>
+        <v>227614</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>46609</v>
+        <v>216125</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>68282</v>
+        <v>237917</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.1982261056672033</v>
+        <v>0.7890792141954123</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.161580544093606</v>
+        <v>0.7492494001216726</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.2367177423352348</v>
+        <v>0.8247968978137565</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>175</v>
+        <v>2</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>118944</v>
+        <v>1284</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>110913</v>
+        <v>0</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>126611</v>
+        <v>4471</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.7839720000098818</v>
+        <v>0.008464803435959931</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.7310392440055646</v>
+        <v>0</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.8345064092620026</v>
+        <v>0.02946808221361957</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>157</v>
+        <v>4</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>108670</v>
+        <v>2378</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>100848</v>
+        <v>616</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>115322</v>
+        <v>5926</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.7947461493555172</v>
+        <v>0.01738812672713651</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.7375426385262301</v>
+        <v>0.004504064889290805</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.8433970866873363</v>
+        <v>0.043340154559706</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>332</v>
+        <v>6</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>227614</v>
+        <v>3662</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>216125</v>
+        <v>1716</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>237917</v>
+        <v>7389</v>
       </c>
       <c r="U6" s="6" t="n">
-        <v>0.7890792141954123</v>
+        <v>0.01269468013738443</v>
       </c>
       <c r="V6" s="6" t="n">
-        <v>0.7492494001216726</v>
+        <v>0.00594815053882774</v>
       </c>
       <c r="W6" s="6" t="n">
-        <v>0.8247968978137565</v>
+        <v>0.0256156654943652</v>
       </c>
     </row>
     <row r="7">
@@ -1014,213 +1014,213 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>7</v>
+        <v>63</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>4747</v>
+        <v>41826</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>2010</v>
+        <v>33024</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>9470</v>
+        <v>51166</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.02244791485608118</v>
+        <v>0.1977987065406616</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.009507684670995309</v>
+        <v>0.156174844118206</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.04478438625709706</v>
+        <v>0.2419704775112381</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>5004</v>
+        <v>39212</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>2383</v>
+        <v>31166</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>9303</v>
+        <v>48488</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.02572649510615601</v>
+        <v>0.2015922245571061</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.01225251811392235</v>
+        <v>0.1602315184599035</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.04782631770353991</v>
+        <v>0.2492820890393596</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>15</v>
+        <v>126</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>9751</v>
+        <v>81037</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>5348</v>
+        <v>67903</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>15672</v>
+        <v>94169</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.02401877440897176</v>
+        <v>0.1996162871885833</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.01317366130192173</v>
+        <v>0.1672640203713665</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.03860387066963637</v>
+        <v>0.2319644268137254</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>63</v>
+        <v>251</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>41826</v>
+        <v>164884</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>33024</v>
+        <v>154748</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>51166</v>
+        <v>174139</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.1977987065406616</v>
+        <v>0.7797533786032572</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.156174844118206</v>
+        <v>0.7318221186888785</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.2419704775112381</v>
+        <v>0.8235242829223671</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>63</v>
+        <v>240</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>39212</v>
+        <v>150293</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>31166</v>
+        <v>140507</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>48488</v>
+        <v>158322</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.2015922245571061</v>
+        <v>0.7726812803367379</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.1602315184599035</v>
+        <v>0.7223661015714143</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.2492820890393596</v>
+        <v>0.8139577755471267</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>126</v>
+        <v>491</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>81037</v>
+        <v>315177</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>67903</v>
+        <v>300733</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>94169</v>
+        <v>328373</v>
       </c>
       <c r="U9" s="6" t="n">
-        <v>0.1996162871885833</v>
+        <v>0.7763649384024449</v>
       </c>
       <c r="V9" s="6" t="n">
-        <v>0.1672640203713665</v>
+        <v>0.7407850141812611</v>
       </c>
       <c r="W9" s="6" t="n">
-        <v>0.2319644268137254</v>
+        <v>0.8088713749018908</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>251</v>
+        <v>7</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>164884</v>
+        <v>4747</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>154748</v>
+        <v>2010</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>174139</v>
+        <v>9470</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.7797533786032572</v>
+        <v>0.02244791485608118</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.7318221186888785</v>
+        <v>0.009507684670995309</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.8235242829223671</v>
+        <v>0.04478438625709706</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>240</v>
+        <v>8</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>150293</v>
+        <v>5004</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>140507</v>
+        <v>2383</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>158322</v>
+        <v>9303</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.7726812803367379</v>
+        <v>0.02572649510615601</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.7223661015714143</v>
+        <v>0.01225251811392235</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.8139577755471267</v>
+        <v>0.04782631770353991</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>491</v>
+        <v>15</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>315177</v>
+        <v>9751</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>300733</v>
+        <v>5348</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>328373</v>
+        <v>15672</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.7763649384024449</v>
+        <v>0.02401877440897176</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.7407850141812611</v>
+        <v>0.01317366130192173</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.8088713749018908</v>
+        <v>0.03860387066963637</v>
       </c>
     </row>
     <row r="11">
@@ -1302,213 +1302,213 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>5</v>
+        <v>63</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>3231</v>
+        <v>38847</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>1282</v>
+        <v>31150</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>7144</v>
+        <v>47587</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.02165880904931872</v>
+        <v>0.2604108381400227</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.008594092698896875</v>
+        <v>0.2088150511989901</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.04789162036464471</v>
+        <v>0.3190024860645428</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>8</v>
+        <v>71</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>4516</v>
+        <v>41614</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>1861</v>
+        <v>33350</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>8563</v>
+        <v>49032</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.03298546847440915</v>
+        <v>0.3039594853715976</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.01359065454997629</v>
+        <v>0.2435926405065194</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.06254648150204234</v>
+        <v>0.3581431917654371</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>13</v>
+        <v>134</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>7747</v>
+        <v>80461</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>4180</v>
+        <v>68656</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>13024</v>
+        <v>92962</v>
       </c>
       <c r="U12" s="6" t="n">
-        <v>0.02707930617395918</v>
+        <v>0.2812515210140775</v>
       </c>
       <c r="V12" s="6" t="n">
-        <v>0.0146122512468762</v>
+        <v>0.2399864547292924</v>
       </c>
       <c r="W12" s="6" t="n">
-        <v>0.04552555170822606</v>
+        <v>0.3249501393468996</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>63</v>
+        <v>163</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>38847</v>
+        <v>107097</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>31150</v>
+        <v>98369</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>47587</v>
+        <v>115406</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.2604108381400227</v>
+        <v>0.7179303528106585</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.2088150511989901</v>
+        <v>0.6594242802609296</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.3190024860645428</v>
+        <v>0.7736363804464823</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>71</v>
+        <v>148</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>41614</v>
+        <v>90777</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>33350</v>
+        <v>82738</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>49032</v>
+        <v>98974</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.3039594853715976</v>
+        <v>0.6630550461539932</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.2435926405065194</v>
+        <v>0.6043390440523524</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.3581431917654371</v>
+        <v>0.7229254595968289</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>134</v>
+        <v>311</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>80461</v>
+        <v>197873</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>68656</v>
+        <v>186084</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>92962</v>
+        <v>210284</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.2812515210140775</v>
+        <v>0.6916691728119633</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.2399864547292924</v>
+        <v>0.6504595094797363</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.3249501393468996</v>
+        <v>0.735050431258891</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>163</v>
+        <v>5</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>107097</v>
+        <v>3231</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>98369</v>
+        <v>1282</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>115406</v>
+        <v>7144</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.7179303528106585</v>
+        <v>0.02165880904931872</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.6594242802609296</v>
+        <v>0.008594092698896875</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.7736363804464823</v>
+        <v>0.04789162036464471</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>148</v>
+        <v>8</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>90777</v>
+        <v>4516</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>82738</v>
+        <v>1861</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>98974</v>
+        <v>8563</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.6630550461539932</v>
+        <v>0.03298546847440915</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.6043390440523524</v>
+        <v>0.01359065454997629</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.7229254595968289</v>
+        <v>0.06254648150204234</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>311</v>
+        <v>13</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>197873</v>
+        <v>7747</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>186084</v>
+        <v>4180</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>210284</v>
+        <v>13024</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.6916691728119633</v>
+        <v>0.02707930617395918</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.6504595094797363</v>
+        <v>0.0146122512468762</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.735050431258891</v>
+        <v>0.04552555170822606</v>
       </c>
     </row>
     <row r="15">
@@ -1590,213 +1590,213 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>7</v>
+        <v>89</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>4691</v>
+        <v>60994</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>2008</v>
+        <v>50917</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>9175</v>
+        <v>71832</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.02264947445572682</v>
+        <v>0.2944749423876575</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.009696601729145592</v>
+        <v>0.2458247195214721</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.04429761766589266</v>
+        <v>0.3467959899708182</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>3</v>
+        <v>76</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>2325</v>
+        <v>57233</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>768</v>
+        <v>47047</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>6589</v>
+        <v>68220</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.01123336278137642</v>
+        <v>0.2764999318815586</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.003712207509921577</v>
+        <v>0.2272898908408316</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.03183414925154334</v>
+        <v>0.3295792619476173</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>10</v>
+        <v>165</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>7017</v>
+        <v>118227</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>3581</v>
+        <v>103495</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>12789</v>
+        <v>133235</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.0169433407238509</v>
+        <v>0.2854904635470972</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.008646268775837587</v>
+        <v>0.2499153138145991</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.03088136831130493</v>
+        <v>0.3217316312861003</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>89</v>
+        <v>209</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>60994</v>
+        <v>141443</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>50917</v>
+        <v>130160</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>71832</v>
+        <v>152197</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.2944749423876575</v>
+        <v>0.6828755831566157</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.2458247195214721</v>
+        <v>0.6283993047136094</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.3467959899708182</v>
+        <v>0.7347939557204858</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>76</v>
+        <v>192</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>57233</v>
+        <v>147432</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>47047</v>
+        <v>136687</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>68220</v>
+        <v>157802</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.2764999318815586</v>
+        <v>0.7122667053370649</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.2272898908408316</v>
+        <v>0.6603573804206747</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.3295792619476173</v>
+        <v>0.7623639369911144</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>165</v>
+        <v>401</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>118227</v>
+        <v>288875</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>103495</v>
+        <v>274009</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>133235</v>
+        <v>303502</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.2854904635470972</v>
+        <v>0.697566195729052</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.2499153138145991</v>
+        <v>0.6616662574867749</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.3217316312861003</v>
+        <v>0.7328855094523714</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>209</v>
+        <v>7</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>141443</v>
+        <v>4691</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>130160</v>
+        <v>2008</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>152197</v>
+        <v>9175</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.6828755831566157</v>
+        <v>0.02264947445572682</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.6283993047136094</v>
+        <v>0.009696601729145592</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.7347939557204858</v>
+        <v>0.04429761766589266</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>192</v>
+        <v>3</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>147432</v>
+        <v>2325</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>136687</v>
+        <v>768</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>157802</v>
+        <v>6589</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.7122667053370649</v>
+        <v>0.01123336278137642</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.6603573804206747</v>
+        <v>0.003712207509921577</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.7623639369911144</v>
+        <v>0.03183414925154334</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>401</v>
+        <v>10</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>288875</v>
+        <v>7017</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>274009</v>
+        <v>3581</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>303502</v>
+        <v>12789</v>
       </c>
       <c r="U18" s="6" t="n">
-        <v>0.697566195729052</v>
+        <v>0.0169433407238509</v>
       </c>
       <c r="V18" s="6" t="n">
-        <v>0.6616662574867749</v>
+        <v>0.008646268775837587</v>
       </c>
       <c r="W18" s="6" t="n">
-        <v>0.7328855094523714</v>
+        <v>0.03088136831130493</v>
       </c>
     </row>
     <row r="19">
@@ -1878,213 +1878,213 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>21</v>
+        <v>262</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>13953</v>
+        <v>173158</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>8673</v>
+        <v>155077</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>20533</v>
+        <v>192328</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.01939364606044573</v>
+        <v>0.2406714509904848</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.01205389154463701</v>
+        <v>0.2155405004282913</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.02853808152769957</v>
+        <v>0.2673151057545288</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>23</v>
+        <v>249</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>14223</v>
+        <v>163746</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>8940</v>
+        <v>146150</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>20426</v>
+        <v>181168</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.02106632777329644</v>
+        <v>0.2425363542128633</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.01324141891628579</v>
+        <v>0.2164728860574858</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.03025468291728948</v>
+        <v>0.2683416773859439</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>44</v>
+        <v>511</v>
       </c>
       <c r="R20" s="5" t="n">
-        <v>28176</v>
+        <v>336904</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>20465</v>
+        <v>310418</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>37257</v>
+        <v>361950</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>0.0202033978295066</v>
+        <v>0.2415742579452369</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>0.01467404925083009</v>
+        <v>0.2225826143972093</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>0.0267145879247149</v>
+        <v>0.2595332328959067</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>262</v>
+        <v>798</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>173158</v>
+        <v>532368</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>155077</v>
+        <v>513235</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>192328</v>
+        <v>551237</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.2406714509904848</v>
+        <v>0.7399349029490695</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.2155405004282913</v>
+        <v>0.7133427101810375</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.2673151057545288</v>
+        <v>0.7661608922029639</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>249</v>
+        <v>737</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>163746</v>
+        <v>497172</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>146150</v>
+        <v>480522</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>181168</v>
+        <v>515664</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.2425363542128633</v>
+        <v>0.7363973180138402</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.2164728860574858</v>
+        <v>0.7117351437053366</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.2683416773859439</v>
+        <v>0.7637877192766752</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>511</v>
+        <v>1535</v>
       </c>
       <c r="R21" s="5" t="n">
-        <v>336904</v>
+        <v>1029540</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>310418</v>
+        <v>1003723</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>361950</v>
+        <v>1057093</v>
       </c>
       <c r="U21" s="6" t="n">
-        <v>0.2415742579452369</v>
+        <v>0.7382223442252565</v>
       </c>
       <c r="V21" s="6" t="n">
-        <v>0.2225826143972093</v>
+        <v>0.7197107979666113</v>
       </c>
       <c r="W21" s="6" t="n">
-        <v>0.2595332328959067</v>
+        <v>0.7579792910117095</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>798</v>
+        <v>21</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>532368</v>
+        <v>13953</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>513235</v>
+        <v>8673</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>551237</v>
+        <v>20533</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.7399349029490695</v>
+        <v>0.01939364606044573</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.7133427101810375</v>
+        <v>0.01205389154463701</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.7661608922029639</v>
+        <v>0.02853808152769957</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>737</v>
+        <v>23</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>497172</v>
+        <v>14223</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>480522</v>
+        <v>8940</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>515664</v>
+        <v>20426</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.7363973180138402</v>
+        <v>0.02106632777329644</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.7117351437053366</v>
+        <v>0.01324141891628579</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.7637877192766752</v>
+        <v>0.03025468291728948</v>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>1535</v>
+        <v>44</v>
       </c>
       <c r="R22" s="5" t="n">
-        <v>1029540</v>
+        <v>28176</v>
       </c>
       <c r="S22" s="5" t="n">
-        <v>1003723</v>
+        <v>20465</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>1057093</v>
+        <v>37257</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>0.7382223442252565</v>
+        <v>0.0202033978295066</v>
       </c>
       <c r="V22" s="6" t="n">
-        <v>0.7197107979666113</v>
+        <v>0.01467404925083009</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>0.7579792910117095</v>
+        <v>0.0267145879247149</v>
       </c>
     </row>
     <row r="23">
@@ -2398,213 +2398,213 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>4687</v>
+        <v>39107</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>1906</v>
+        <v>31110</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>9694</v>
+        <v>48718</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.03043062796417147</v>
+        <v>0.2539147307917282</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.01237211399711374</v>
+        <v>0.2019891943984826</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.06294127613106643</v>
+        <v>0.3163185773542268</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>2251</v>
+        <v>29929</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>658</v>
+        <v>22368</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>6273</v>
+        <v>39529</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.01615433379908899</v>
+        <v>0.2147660484150911</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.004722696960674276</v>
+        <v>0.1605100375811673</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.04501398341457575</v>
+        <v>0.283654366837409</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>9</v>
+        <v>94</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>6938</v>
+        <v>69036</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>3499</v>
+        <v>56611</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>13831</v>
+        <v>81459</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.02364915475131071</v>
+        <v>0.2353184663980388</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.01192687675334455</v>
+        <v>0.1929670308815482</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.04714406468676834</v>
+        <v>0.2776649073769982</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>54</v>
+        <v>150</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>39107</v>
+        <v>110222</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>31110</v>
+        <v>100092</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>48718</v>
+        <v>118888</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.2539147307917282</v>
+        <v>0.7156546412441003</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.2019891943984826</v>
+        <v>0.6498801461095772</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.3163185773542268</v>
+        <v>0.7719167623952193</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>40</v>
+        <v>146</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>29929</v>
+        <v>107177</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>22368</v>
+        <v>97772</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>39529</v>
+        <v>115158</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.2147660484150911</v>
+        <v>0.7690796177858199</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.1605100375811673</v>
+        <v>0.7015959127468828</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.283654366837409</v>
+        <v>0.8263527571355388</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>94</v>
+        <v>296</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>69036</v>
+        <v>217399</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>56611</v>
+        <v>204369</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>81459</v>
+        <v>230486</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.2353184663980388</v>
+        <v>0.7410323788506504</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.1929670308815482</v>
+        <v>0.6966186604339836</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.2776649073769982</v>
+        <v>0.7856414005320727</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>110222</v>
+        <v>4687</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>100092</v>
+        <v>1906</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>118888</v>
+        <v>9694</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.7156546412441003</v>
+        <v>0.03043062796417147</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.6498801461095772</v>
+        <v>0.01237211399711374</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.7719167623952193</v>
+        <v>0.06294127613106643</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>107177</v>
+        <v>2251</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>97772</v>
+        <v>658</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>115158</v>
+        <v>6273</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.7690796177858199</v>
+        <v>0.01615433379908899</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.7015959127468828</v>
+        <v>0.004722696960674276</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.8263527571355388</v>
+        <v>0.04501398341457575</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>296</v>
+        <v>9</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>217399</v>
+        <v>6938</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>204369</v>
+        <v>3499</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>230486</v>
+        <v>13831</v>
       </c>
       <c r="U6" s="6" t="n">
-        <v>0.7410323788506504</v>
+        <v>0.02364915475131071</v>
       </c>
       <c r="V6" s="6" t="n">
-        <v>0.6966186604339836</v>
+        <v>0.01192687675334455</v>
       </c>
       <c r="W6" s="6" t="n">
-        <v>0.7856414005320727</v>
+        <v>0.04714406468676834</v>
       </c>
     </row>
     <row r="7">
@@ -2686,213 +2686,213 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>8436</v>
+        <v>55156</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>4695</v>
+        <v>45787</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>14742</v>
+        <v>65923</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.03780270183789259</v>
+        <v>0.2471531975519226</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.02103950081708997</v>
+        <v>0.2051705768112167</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.06605886131617476</v>
+        <v>0.2953978906965063</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>11</v>
+        <v>78</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>6902</v>
+        <v>48765</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>3704</v>
+        <v>39448</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>12462</v>
+        <v>58104</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.03344681677440173</v>
+        <v>0.2363134625326572</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.01794777610954382</v>
+        <v>0.1911622806959332</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.06039228155839782</v>
+        <v>0.2815668682015044</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>23</v>
+        <v>159</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>15338</v>
+        <v>103922</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>10452</v>
+        <v>90346</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>22592</v>
+        <v>118966</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.03570999007202701</v>
+        <v>0.2419454290541233</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.02433456771147024</v>
+        <v>0.2103401312172287</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.05259871093317891</v>
+        <v>0.2769705880994796</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>81</v>
+        <v>230</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>55156</v>
+        <v>159574</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>45787</v>
+        <v>147642</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>65923</v>
+        <v>169932</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.2471531975519226</v>
+        <v>0.7150441006101849</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.2051705768112167</v>
+        <v>0.6615763845623187</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.2953978906965063</v>
+        <v>0.7614559131641542</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>78</v>
+        <v>230</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>48765</v>
+        <v>150691</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>39448</v>
+        <v>140759</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>58104</v>
+        <v>160229</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.2363134625326572</v>
+        <v>0.7302397206929411</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.1911622806959332</v>
+        <v>0.6821092323241339</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.2815668682015044</v>
+        <v>0.7764610209354875</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>159</v>
+        <v>460</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>103922</v>
+        <v>310265</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>90346</v>
+        <v>295546</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>118966</v>
+        <v>324617</v>
       </c>
       <c r="U9" s="6" t="n">
-        <v>0.2419454290541233</v>
+        <v>0.7223445808738497</v>
       </c>
       <c r="V9" s="6" t="n">
-        <v>0.2103401312172287</v>
+        <v>0.688076307344509</v>
       </c>
       <c r="W9" s="6" t="n">
-        <v>0.2769705880994796</v>
+        <v>0.75575847244072</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>230</v>
+        <v>12</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>159574</v>
+        <v>8436</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>147642</v>
+        <v>4695</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>169932</v>
+        <v>14742</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.7150441006101849</v>
+        <v>0.03780270183789259</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.6615763845623187</v>
+        <v>0.02103950081708997</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.7614559131641542</v>
+        <v>0.06605886131617476</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>230</v>
+        <v>11</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>150691</v>
+        <v>6902</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>140759</v>
+        <v>3704</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>160229</v>
+        <v>12462</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.7302397206929411</v>
+        <v>0.03344681677440173</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.6821092323241339</v>
+        <v>0.01794777610954382</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.7764610209354875</v>
+        <v>0.06039228155839782</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>460</v>
+        <v>23</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>310265</v>
+        <v>15338</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>295546</v>
+        <v>10452</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>324617</v>
+        <v>22592</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.7223445808738497</v>
+        <v>0.03570999007202701</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.688076307344509</v>
+        <v>0.02433456771147024</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.75575847244072</v>
+        <v>0.05259871093317891</v>
       </c>
     </row>
     <row r="11">
@@ -2974,213 +2974,213 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>5146</v>
+        <v>41356</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>2498</v>
+        <v>32770</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>9748</v>
+        <v>50745</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.03089268231881722</v>
+        <v>0.2482494665308323</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.01499742762399426</v>
+        <v>0.1967106847330655</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.05851537869593218</v>
+        <v>0.3046049194302491</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>6</v>
+        <v>76</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>4243</v>
+        <v>47832</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>1767</v>
+        <v>39331</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>9011</v>
+        <v>57061</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.02742583355178196</v>
+        <v>0.3091904635739307</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.01142482395168378</v>
+        <v>0.2542407207687452</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.05825015720347829</v>
+        <v>0.3688495677016591</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>14</v>
+        <v>139</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>9389</v>
+        <v>89188</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>5444</v>
+        <v>77409</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>15621</v>
+        <v>102041</v>
       </c>
       <c r="U12" s="6" t="n">
-        <v>0.02922341338613575</v>
+        <v>0.27759222703944</v>
       </c>
       <c r="V12" s="6" t="n">
-        <v>0.01694403641640576</v>
+        <v>0.2409299424028045</v>
       </c>
       <c r="W12" s="6" t="n">
-        <v>0.04861804042437044</v>
+        <v>0.3175937766581282</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>63</v>
+        <v>185</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>41356</v>
+        <v>120089</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>32770</v>
+        <v>109969</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>50745</v>
+        <v>128609</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.2482494665308323</v>
+        <v>0.7208578511503505</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.1967106847330655</v>
+        <v>0.66010770710735</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.3046049194302491</v>
+        <v>0.7720017825925489</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>76</v>
+        <v>159</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>47832</v>
+        <v>102626</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>39331</v>
+        <v>92792</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>57061</v>
+        <v>111223</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.3091904635739307</v>
+        <v>0.6633837028742873</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.2542407207687452</v>
+        <v>0.5998130631845286</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.3688495677016591</v>
+        <v>0.7189535829030942</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>139</v>
+        <v>344</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>89188</v>
+        <v>222715</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>77409</v>
+        <v>210135</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>102041</v>
+        <v>234863</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.27759222703944</v>
+        <v>0.6931843595744243</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.2409299424028045</v>
+        <v>0.6540292868323605</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.3175937766581282</v>
+        <v>0.7309925171898888</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>185</v>
+        <v>8</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>120089</v>
+        <v>5146</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>109969</v>
+        <v>2498</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>128609</v>
+        <v>9748</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.7208578511503505</v>
+        <v>0.03089268231881722</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.66010770710735</v>
+        <v>0.01499742762399426</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.7720017825925489</v>
+        <v>0.05851537869593218</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>159</v>
+        <v>6</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>102626</v>
+        <v>4243</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>92792</v>
+        <v>1767</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>111223</v>
+        <v>9011</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.6633837028742873</v>
+        <v>0.02742583355178196</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.5998130631845286</v>
+        <v>0.01142482395168378</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.7189535829030942</v>
+        <v>0.05825015720347829</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>344</v>
+        <v>14</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>222715</v>
+        <v>9389</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>210135</v>
+        <v>5444</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>234863</v>
+        <v>15621</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.6931843595744243</v>
+        <v>0.02922341338613575</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.6540292868323605</v>
+        <v>0.01694403641640576</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.7309925171898888</v>
+        <v>0.04861804042437044</v>
       </c>
     </row>
     <row r="15">
@@ -3262,213 +3262,213 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>5</v>
+        <v>77</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>3390</v>
+        <v>56936</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>1302</v>
+        <v>46870</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>7950</v>
+        <v>68560</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.01626941128842375</v>
+        <v>0.2732107921750794</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.006249400002299617</v>
+        <v>0.2249090479809404</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.03815068935383928</v>
+        <v>0.3289869112606642</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>5</v>
+        <v>73</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>4060</v>
+        <v>54996</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>1482</v>
+        <v>44538</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>9047</v>
+        <v>66305</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.01937922386983343</v>
+        <v>0.2624923320628804</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.007073850798501475</v>
+        <v>0.2125785544840642</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.04318320434805176</v>
+        <v>0.316472820817311</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>7451</v>
+        <v>111932</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>3872</v>
+        <v>96770</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>13339</v>
+        <v>127399</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.01782847488208218</v>
+        <v>0.2678372333178975</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.009264638968842177</v>
+        <v>0.2315568545521594</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.03191882467694968</v>
+        <v>0.3048487007579202</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>77</v>
+        <v>201</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>56936</v>
+        <v>148069</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>46870</v>
+        <v>136477</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>68560</v>
+        <v>158396</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.2732107921750794</v>
+        <v>0.7105197965364969</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.2249090479809404</v>
+        <v>0.6548918985438575</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.3289869112606642</v>
+        <v>0.7600732817680952</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>73</v>
+        <v>196</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>54996</v>
+        <v>150457</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>44538</v>
+        <v>139040</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>66305</v>
+        <v>161653</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.2624923320628804</v>
+        <v>0.7181284440672862</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.2125785544840642</v>
+        <v>0.6636361760772338</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.316472820817311</v>
+        <v>0.7715640009407517</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>150</v>
+        <v>397</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>111932</v>
+        <v>298527</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>96770</v>
+        <v>282344</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>127399</v>
+        <v>315155</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.2678372333178975</v>
+        <v>0.7143342918000203</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.2315568545521594</v>
+        <v>0.6756116426121154</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.3048487007579202</v>
+        <v>0.7541233862587793</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>201</v>
+        <v>5</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>148069</v>
+        <v>3390</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>136477</v>
+        <v>1302</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>158396</v>
+        <v>7950</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.7105197965364969</v>
+        <v>0.01626941128842375</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.6548918985438575</v>
+        <v>0.006249400002299617</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.7600732817680952</v>
+        <v>0.03815068935383928</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>196</v>
+        <v>5</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>150457</v>
+        <v>4060</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>139040</v>
+        <v>1482</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>161653</v>
+        <v>9047</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.7181284440672862</v>
+        <v>0.01937922386983343</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.6636361760772338</v>
+        <v>0.007073850798501475</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.7715640009407517</v>
+        <v>0.04318320434805176</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>397</v>
+        <v>10</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>298527</v>
+        <v>7451</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>282344</v>
+        <v>3872</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>315155</v>
+        <v>13339</v>
       </c>
       <c r="U18" s="6" t="n">
-        <v>0.7143342918000203</v>
+        <v>0.01782847488208218</v>
       </c>
       <c r="V18" s="6" t="n">
-        <v>0.6756116426121154</v>
+        <v>0.009264638968842177</v>
       </c>
       <c r="W18" s="6" t="n">
-        <v>0.7541233862587793</v>
+        <v>0.03191882467694968</v>
       </c>
     </row>
     <row r="19">
@@ -3550,213 +3550,213 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>31</v>
+        <v>275</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>21660</v>
+        <v>192556</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>15299</v>
+        <v>173788</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>31292</v>
+        <v>211642</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.0287967386144427</v>
+        <v>0.2560000077441857</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.02033989782050098</v>
+        <v>0.2310486856727014</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.04160258244750865</v>
+        <v>0.2813744590352787</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>25</v>
+        <v>267</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>17456</v>
+        <v>181522</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>11542</v>
+        <v>163119</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>25465</v>
+        <v>200197</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.02458870967016811</v>
+        <v>0.2556902739256171</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.0162584324010649</v>
+        <v>0.2297686792260264</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.03587048487263438</v>
+        <v>0.2819956789192741</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>56</v>
+        <v>542</v>
       </c>
       <c r="R20" s="5" t="n">
-        <v>39116</v>
+        <v>374078</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>29395</v>
+        <v>346260</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>50222</v>
+        <v>399492</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>0.02675351171362498</v>
+        <v>0.2558496151307856</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>0.0201045068602867</v>
+        <v>0.236823849601798</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>0.03434890626967004</v>
+        <v>0.2732314695523477</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>275</v>
+        <v>766</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>192556</v>
+        <v>537955</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>173788</v>
+        <v>516946</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>211642</v>
+        <v>557406</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.2560000077441857</v>
+        <v>0.7152032536413716</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.2310486856727014</v>
+        <v>0.6872713674420108</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.2813744590352787</v>
+        <v>0.7410624134996078</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>267</v>
+        <v>731</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>181522</v>
+        <v>510951</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>163119</v>
+        <v>490900</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>200197</v>
+        <v>528676</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.2556902739256171</v>
+        <v>0.7197210164042148</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.2297686792260264</v>
+        <v>0.6914777132122374</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.2819956789192741</v>
+        <v>0.7446884119296957</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>542</v>
+        <v>1497</v>
       </c>
       <c r="R21" s="5" t="n">
-        <v>374078</v>
+        <v>1048906</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>346260</v>
+        <v>1019157</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>399492</v>
+        <v>1074094</v>
       </c>
       <c r="U21" s="6" t="n">
-        <v>0.2558496151307856</v>
+        <v>0.7173968731555894</v>
       </c>
       <c r="V21" s="6" t="n">
-        <v>0.236823849601798</v>
+        <v>0.6970501449409208</v>
       </c>
       <c r="W21" s="6" t="n">
-        <v>0.2732314695523477</v>
+        <v>0.7346239874790342</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>766</v>
+        <v>31</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>537955</v>
+        <v>21660</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>516946</v>
+        <v>15299</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>557406</v>
+        <v>31292</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.7152032536413716</v>
+        <v>0.0287967386144427</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.6872713674420108</v>
+        <v>0.02033989782050098</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.7410624134996078</v>
+        <v>0.04160258244750865</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>731</v>
+        <v>25</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>510951</v>
+        <v>17456</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>490900</v>
+        <v>11542</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>528676</v>
+        <v>25465</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.7197210164042148</v>
+        <v>0.02458870967016811</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.6914777132122374</v>
+        <v>0.0162584324010649</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.7446884119296957</v>
+        <v>0.03587048487263438</v>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>1497</v>
+        <v>56</v>
       </c>
       <c r="R22" s="5" t="n">
-        <v>1048906</v>
+        <v>39116</v>
       </c>
       <c r="S22" s="5" t="n">
-        <v>1019157</v>
+        <v>29395</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>1074094</v>
+        <v>50222</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>0.7173968731555894</v>
+        <v>0.02675351171362498</v>
       </c>
       <c r="V22" s="6" t="n">
-        <v>0.6970501449409208</v>
+        <v>0.0201045068602867</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>0.7346239874790342</v>
+        <v>0.03434890626967004</v>
       </c>
     </row>
     <row r="23">
@@ -4070,213 +4070,213 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>2814</v>
+        <v>40231</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>690</v>
+        <v>31541</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>7141</v>
+        <v>50399</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.01900294143180835</v>
+        <v>0.2716938654915212</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.004659046543364474</v>
+        <v>0.2130033988964099</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.04822205368135119</v>
+        <v>0.3403581531058017</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>3587</v>
+        <v>23318</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>1171</v>
+        <v>16731</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>7936</v>
+        <v>31357</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.02682810652352036</v>
+        <v>0.1743945438772005</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.008759983092447242</v>
+        <v>0.125130538001696</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.05935593459971333</v>
+        <v>0.2345216517138764</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>9</v>
+        <v>89</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>6401</v>
+        <v>63549</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>2952</v>
+        <v>52924</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>11608</v>
+        <v>76560</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.02271600934087449</v>
+        <v>0.2255250007550204</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.01047498739754357</v>
+        <v>0.1878171337995851</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.04119433470130402</v>
+        <v>0.2716983984593918</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>55</v>
+        <v>136</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>40231</v>
+        <v>105031</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>31541</v>
+        <v>94558</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>50399</v>
+        <v>113699</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.2716938654915212</v>
+        <v>0.7093031930766704</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.2130033988964099</v>
+        <v>0.6385781461468264</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.3403581531058017</v>
+        <v>0.7678424635104724</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>34</v>
+        <v>148</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>23318</v>
+        <v>106802</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>16731</v>
+        <v>98686</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>31357</v>
+        <v>113894</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.1743945438772005</v>
+        <v>0.7987773495992792</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.125130538001696</v>
+        <v>0.7380776134808504</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.2345216517138764</v>
+        <v>0.8518165658676495</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>89</v>
+        <v>284</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>63549</v>
+        <v>211833</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>52924</v>
+        <v>199123</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>76560</v>
+        <v>223492</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.2255250007550204</v>
+        <v>0.7517589899041052</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.1878171337995851</v>
+        <v>0.7066522148565352</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.2716983984593918</v>
+        <v>0.793135884549993</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>136</v>
+        <v>4</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>105031</v>
+        <v>2814</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>94558</v>
+        <v>690</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>113699</v>
+        <v>7141</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.7093031930766704</v>
+        <v>0.01900294143180835</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.6385781461468264</v>
+        <v>0.004659046543364474</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.7678424635104724</v>
+        <v>0.04822205368135119</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>148</v>
+        <v>5</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>106802</v>
+        <v>3587</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>98686</v>
+        <v>1171</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>113894</v>
+        <v>7936</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.7987773495992792</v>
+        <v>0.02682810652352036</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.7380776134808504</v>
+        <v>0.008759983092447242</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.8518165658676495</v>
+        <v>0.05935593459971333</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>284</v>
+        <v>9</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>211833</v>
+        <v>6401</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>199123</v>
+        <v>2952</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>223492</v>
+        <v>11608</v>
       </c>
       <c r="U6" s="6" t="n">
-        <v>0.7517589899041052</v>
+        <v>0.02271600934087449</v>
       </c>
       <c r="V6" s="6" t="n">
-        <v>0.7066522148565352</v>
+        <v>0.01047498739754357</v>
       </c>
       <c r="W6" s="6" t="n">
-        <v>0.793135884549993</v>
+        <v>0.04119433470130402</v>
       </c>
     </row>
     <row r="7">
@@ -4358,213 +4358,213 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>5</v>
+        <v>112</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>3205</v>
+        <v>75686</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>1238</v>
+        <v>65562</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>7098</v>
+        <v>87533</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.01432563530415565</v>
+        <v>0.3382863730399846</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.00553258718220607</v>
+        <v>0.2930363789805073</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.03172513637686975</v>
+        <v>0.3912396100783413</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>7</v>
+        <v>113</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>3920</v>
+        <v>69517</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>1648</v>
+        <v>59100</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>7687</v>
+        <v>81095</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.01901666434832624</v>
+        <v>0.3372192258254367</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.007994812122385465</v>
+        <v>0.2866874638180176</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.0372881294502812</v>
+        <v>0.3933844902484252</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>12</v>
+        <v>225</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>7125</v>
+        <v>145203</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>3953</v>
+        <v>129671</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>12510</v>
+        <v>160783</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.01657519679960052</v>
+        <v>0.337774627480276</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.009195103444567455</v>
+        <v>0.3016454169962988</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.02910125345182239</v>
+        <v>0.3740175914600707</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>112</v>
+        <v>214</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>75686</v>
+        <v>144842</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>65562</v>
+        <v>132242</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>87533</v>
+        <v>155451</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.3382863730399846</v>
+        <v>0.6473879916558597</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.2930363789805073</v>
+        <v>0.5910691940150495</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.3912396100783413</v>
+        <v>0.694806589186082</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>113</v>
+        <v>212</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>69517</v>
+        <v>132710</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>59100</v>
+        <v>121304</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>81095</v>
+        <v>142733</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.3372192258254367</v>
+        <v>0.6437641098262371</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.2866874638180176</v>
+        <v>0.5884347882087733</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.3933844902484252</v>
+        <v>0.6923861051682522</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>225</v>
+        <v>426</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>145203</v>
+        <v>277552</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>129671</v>
+        <v>260853</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>160783</v>
+        <v>292481</v>
       </c>
       <c r="U9" s="6" t="n">
-        <v>0.337774627480276</v>
+        <v>0.6456501757201234</v>
       </c>
       <c r="V9" s="6" t="n">
-        <v>0.3016454169962988</v>
+        <v>0.6068047595674662</v>
       </c>
       <c r="W9" s="6" t="n">
-        <v>0.3740175914600707</v>
+        <v>0.6803780427110868</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>214</v>
+        <v>5</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>144842</v>
+        <v>3205</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>132242</v>
+        <v>1238</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>155451</v>
+        <v>7098</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.6473879916558597</v>
+        <v>0.01432563530415565</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.5910691940150495</v>
+        <v>0.00553258718220607</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.694806589186082</v>
+        <v>0.03172513637686975</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>212</v>
+        <v>7</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>132710</v>
+        <v>3920</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>121304</v>
+        <v>1648</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>142733</v>
+        <v>7687</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.6437641098262371</v>
+        <v>0.01901666434832624</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.5884347882087733</v>
+        <v>0.007994812122385465</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.6923861051682522</v>
+        <v>0.0372881294502812</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>426</v>
+        <v>12</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>277552</v>
+        <v>7125</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>260853</v>
+        <v>3953</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>292481</v>
+        <v>12510</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.6456501757201234</v>
+        <v>0.01657519679960052</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.6068047595674662</v>
+        <v>0.009195103444567455</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.6803780427110868</v>
+        <v>0.02910125345182239</v>
       </c>
     </row>
     <row r="11">
@@ -4646,213 +4646,213 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>1939</v>
+        <v>54035</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>629</v>
+        <v>44931</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>5219</v>
+        <v>63655</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.01179849039847308</v>
+        <v>0.3287281015181447</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.003828499501103541</v>
+        <v>0.2733388565227033</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.03174800861872037</v>
+        <v>0.3872496658916236</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>4638</v>
+        <v>45816</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>1814</v>
+        <v>38152</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>8818</v>
+        <v>55248</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.03023701637728696</v>
+        <v>0.2986829417602818</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.01182303965012834</v>
+        <v>0.2487233743214296</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.05748933901114538</v>
+        <v>0.3601721172138928</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>12</v>
+        <v>157</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>6578</v>
+        <v>99851</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>3537</v>
+        <v>86598</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>11483</v>
+        <v>113942</v>
       </c>
       <c r="U12" s="6" t="n">
-        <v>0.02069905810493457</v>
+        <v>0.314224828372364</v>
       </c>
       <c r="V12" s="6" t="n">
-        <v>0.01113144721735288</v>
+        <v>0.2725182608327239</v>
       </c>
       <c r="W12" s="6" t="n">
-        <v>0.03613638648896387</v>
+        <v>0.3585677096937774</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>54035</v>
+        <v>108402</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>44931</v>
+        <v>98051</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>63655</v>
+        <v>117568</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.3287281015181447</v>
+        <v>0.6594734080833823</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.2733388565227033</v>
+        <v>0.5965031426500447</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.3872496658916236</v>
+        <v>0.7152349180167639</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>77</v>
+        <v>169</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>45816</v>
+        <v>102938</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>38152</v>
+        <v>92844</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>55248</v>
+        <v>110911</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.2986829417602818</v>
+        <v>0.6710800418624312</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.2487233743214296</v>
+        <v>0.6052729172945339</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.3601721172138928</v>
+        <v>0.7230591519263783</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>157</v>
+        <v>329</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>99851</v>
+        <v>211341</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>86598</v>
+        <v>197052</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>113942</v>
+        <v>224429</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.314224828372364</v>
+        <v>0.6650761135227015</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.2725182608327239</v>
+        <v>0.6201113760714082</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.3585677096937774</v>
+        <v>0.7062658208553942</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>160</v>
+        <v>4</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>108402</v>
+        <v>1939</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>98051</v>
+        <v>629</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>117568</v>
+        <v>5219</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.6594734080833823</v>
+        <v>0.01179849039847308</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.5965031426500447</v>
+        <v>0.003828499501103541</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.7152349180167639</v>
+        <v>0.03174800861872037</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>169</v>
+        <v>8</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>102938</v>
+        <v>4638</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>92844</v>
+        <v>1814</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>110911</v>
+        <v>8818</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.6710800418624312</v>
+        <v>0.03023701637728696</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.6052729172945339</v>
+        <v>0.01182303965012834</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.7230591519263783</v>
+        <v>0.05748933901114538</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>329</v>
+        <v>12</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>211341</v>
+        <v>6578</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>197052</v>
+        <v>3537</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>224429</v>
+        <v>11483</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.6650761135227015</v>
+        <v>0.02069905810493457</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.6201113760714082</v>
+        <v>0.01113144721735288</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.7062658208553942</v>
+        <v>0.03613638648896387</v>
       </c>
     </row>
     <row r="15">
@@ -4934,205 +4934,205 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>5</v>
+        <v>88</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>3414</v>
+        <v>62641</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>1299</v>
+        <v>52488</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>7613</v>
+        <v>73526</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.01689863970376901</v>
+        <v>0.310016311521363</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.006429945824301449</v>
+        <v>0.2597706965985992</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.03767952652290957</v>
+        <v>0.3638878068389364</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="5" t="inlineStr"/>
-      <c r="M16" s="5" t="inlineStr"/>
+        <v>67863</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>56442</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>79913</v>
+      </c>
       <c r="N16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="6" t="inlineStr"/>
-      <c r="P16" s="6" t="inlineStr"/>
+        <v>0.3294220082779033</v>
+      </c>
+      <c r="O16" s="6" t="n">
+        <v>0.2739799014670473</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v>0.3879127987231059</v>
+      </c>
       <c r="Q16" s="5" t="n">
-        <v>5</v>
+        <v>180</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>3414</v>
+        <v>130504</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>1285</v>
+        <v>114753</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>7408</v>
+        <v>147406</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.008367509263845366</v>
+        <v>0.3198131077848352</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.003149037674980694</v>
+        <v>0.2812127434715673</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.01815404753268033</v>
+        <v>0.3612328009096309</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>88</v>
+        <v>192</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>62641</v>
+        <v>136001</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>52488</v>
+        <v>124865</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>73526</v>
+        <v>146939</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.310016311521363</v>
+        <v>0.673085048774868</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.2597706965985992</v>
+        <v>0.6179745308997343</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.3638878068389364</v>
+        <v>0.727220852300494</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>92</v>
+        <v>187</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>67863</v>
+        <v>138144</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>56442</v>
+        <v>126094</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>79913</v>
+        <v>149565</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.3294220082779033</v>
+        <v>0.6705779917220968</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.2739799014670473</v>
+        <v>0.6120872012768944</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.3879127987231059</v>
+        <v>0.726020098532953</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>180</v>
+        <v>379</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>130504</v>
+        <v>274145</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>114753</v>
+        <v>257011</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>147406</v>
+        <v>289459</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.3198131077848352</v>
+        <v>0.6718193829513194</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.2812127434715673</v>
+        <v>0.6298314803260504</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.3612328009096309</v>
+        <v>0.7093489071896936</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>192</v>
+        <v>5</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>136001</v>
+        <v>3414</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>124865</v>
+        <v>1299</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>146939</v>
+        <v>7613</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.673085048774868</v>
+        <v>0.01689863970376901</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.6179745308997343</v>
+        <v>0.006429945824301449</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.727220852300494</v>
+        <v>0.03767952652290957</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>138144</v>
-      </c>
-      <c r="L18" s="5" t="n">
-        <v>126094</v>
-      </c>
-      <c r="M18" s="5" t="n">
-        <v>149565</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L18" s="5" t="inlineStr"/>
+      <c r="M18" s="5" t="inlineStr"/>
       <c r="N18" s="6" t="n">
-        <v>0.6705779917220968</v>
-      </c>
-      <c r="O18" s="6" t="n">
-        <v>0.6120872012768944</v>
-      </c>
-      <c r="P18" s="6" t="n">
-        <v>0.726020098532953</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O18" s="6" t="inlineStr"/>
+      <c r="P18" s="6" t="inlineStr"/>
       <c r="Q18" s="5" t="n">
-        <v>379</v>
+        <v>5</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>274145</v>
+        <v>3414</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>257011</v>
+        <v>1285</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>289459</v>
+        <v>7408</v>
       </c>
       <c r="U18" s="6" t="n">
-        <v>0.6718193829513194</v>
+        <v>0.008367509263845366</v>
       </c>
       <c r="V18" s="6" t="n">
-        <v>0.6298314803260504</v>
+        <v>0.003149037674980694</v>
       </c>
       <c r="W18" s="6" t="n">
-        <v>0.7093489071896936</v>
+        <v>0.01815404753268033</v>
       </c>
     </row>
     <row r="19">
@@ -5214,213 +5214,213 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>18</v>
+        <v>335</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>11373</v>
+        <v>232593</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>6534</v>
+        <v>211213</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>17383</v>
+        <v>253967</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.01540533868527224</v>
+        <v>0.3150635773624768</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.008850896009006877</v>
+        <v>0.2861024106694964</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.02354584038101045</v>
+        <v>0.3440162031320989</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>20</v>
+        <v>316</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>12145</v>
+        <v>206513</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>7840</v>
+        <v>185452</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>18275</v>
+        <v>225030</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.01736918897859021</v>
+        <v>0.2953341816490889</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.0112119473229022</v>
+        <v>0.2652139349537481</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.02613524002767794</v>
+        <v>0.3218151736648645</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>38</v>
+        <v>651</v>
       </c>
       <c r="R20" s="5" t="n">
-        <v>23518</v>
+        <v>439106</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>17054</v>
+        <v>413010</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>32294</v>
+        <v>468639</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>0.01636063138259591</v>
+        <v>0.3054664366273929</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>0.01186368418093788</v>
+        <v>0.2873125050273043</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>0.02246525665392955</v>
+        <v>0.326011047099263</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>335</v>
+        <v>702</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>232593</v>
+        <v>494276</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>211213</v>
+        <v>473777</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>253967</v>
+        <v>515717</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.3150635773624768</v>
+        <v>0.6695310839522509</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.2861024106694964</v>
+        <v>0.6417632730683875</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.3440162031320989</v>
+        <v>0.6985747199617873</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>316</v>
+        <v>716</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>206513</v>
+        <v>480594</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>185452</v>
+        <v>461458</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>225030</v>
+        <v>500683</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.2953341816490889</v>
+        <v>0.6872966293723209</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.2652139349537481</v>
+        <v>0.6599298932045679</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.3218151736648645</v>
+        <v>0.7160248723910149</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>651</v>
+        <v>1418</v>
       </c>
       <c r="R21" s="5" t="n">
-        <v>439106</v>
+        <v>974870</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>413010</v>
+        <v>945109</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>468639</v>
+        <v>1001563</v>
       </c>
       <c r="U21" s="6" t="n">
-        <v>0.3054664366273929</v>
+        <v>0.6781729319900112</v>
       </c>
       <c r="V21" s="6" t="n">
-        <v>0.2873125050273043</v>
+        <v>0.6574696323566337</v>
       </c>
       <c r="W21" s="6" t="n">
-        <v>0.326011047099263</v>
+        <v>0.6967418884415597</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>702</v>
+        <v>18</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>494276</v>
+        <v>11373</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>473777</v>
+        <v>6534</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>515717</v>
+        <v>17383</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.6695310839522509</v>
+        <v>0.01540533868527224</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.6417632730683875</v>
+        <v>0.008850896009006877</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.6985747199617873</v>
+        <v>0.02354584038101045</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>716</v>
+        <v>20</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>480594</v>
+        <v>12145</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>461458</v>
+        <v>7840</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>500683</v>
+        <v>18275</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.6872966293723209</v>
+        <v>0.01736918897859021</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.6599298932045679</v>
+        <v>0.0112119473229022</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.7160248723910149</v>
+        <v>0.02613524002767794</v>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>1418</v>
+        <v>38</v>
       </c>
       <c r="R22" s="5" t="n">
-        <v>974870</v>
+        <v>23518</v>
       </c>
       <c r="S22" s="5" t="n">
-        <v>945109</v>
+        <v>17054</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>1001563</v>
+        <v>32294</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>0.6781729319900112</v>
+        <v>0.01636063138259591</v>
       </c>
       <c r="V22" s="6" t="n">
-        <v>0.6574696323566337</v>
+        <v>0.01186368418093788</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>0.6967418884415597</v>
+        <v>0.02246525665392955</v>
       </c>
     </row>
     <row r="23">
@@ -5734,205 +5734,205 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
+        <v>34072</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>25359</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>43559</v>
+      </c>
       <c r="G4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="6" t="inlineStr"/>
-      <c r="I4" s="6" t="inlineStr"/>
+        <v>0.2741094178859896</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.204012882456875</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.3504315936151702</v>
+      </c>
       <c r="J4" s="5" t="n">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>751</v>
+        <v>32051</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>0</v>
+        <v>24578</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>4455</v>
+        <v>39706</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.006292122552120258</v>
+        <v>0.2685410621539764</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0</v>
+        <v>0.2059285282163043</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.0373281399264106</v>
+        <v>0.3326783425168935</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>1</v>
+        <v>119</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>751</v>
+        <v>66123</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>0</v>
+        <v>53034</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>3779</v>
+        <v>77969</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.003082180784362822</v>
+        <v>0.2713817725015359</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0</v>
+        <v>0.2176602163121165</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.01550981901009978</v>
+        <v>0.3199983302210235</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>58</v>
+        <v>112</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>34072</v>
+        <v>90228</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>25359</v>
+        <v>80741</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>43559</v>
+        <v>98941</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.2741094178859896</v>
+        <v>0.7258905821140105</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.204012882456875</v>
+        <v>0.6495684063848299</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.3504315936151702</v>
+        <v>0.795987117543125</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>61</v>
+        <v>131</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>32051</v>
+        <v>86551</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>24578</v>
+        <v>78886</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>39706</v>
+        <v>93803</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.2685410621539764</v>
+        <v>0.7251668152939031</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.2059285282163043</v>
+        <v>0.6609491709067672</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.3326783425168935</v>
+        <v>0.7859298663102608</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>119</v>
+        <v>243</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>66123</v>
+        <v>176779</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>53034</v>
+        <v>164786</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>77969</v>
+        <v>190071</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.2713817725015359</v>
+        <v>0.7255360467141013</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.2176602163121165</v>
+        <v>0.6763159772921959</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.3199983302210235</v>
+        <v>0.7800889879880161</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>90228</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>80741</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>98941</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
       <c r="G6" s="6" t="n">
-        <v>0.7258905821140105</v>
-      </c>
-      <c r="H6" s="6" t="n">
-        <v>0.6495684063848299</v>
-      </c>
-      <c r="I6" s="6" t="n">
-        <v>0.795987117543125</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
       <c r="J6" s="5" t="n">
-        <v>131</v>
+        <v>1</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>86551</v>
+        <v>751</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>78886</v>
+        <v>0</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>93803</v>
+        <v>4455</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.7251668152939031</v>
+        <v>0.006292122552120258</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.6609491709067672</v>
+        <v>0</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.7859298663102608</v>
+        <v>0.0373281399264106</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>243</v>
+        <v>1</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>176779</v>
+        <v>751</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>164786</v>
+        <v>0</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>190071</v>
+        <v>3779</v>
       </c>
       <c r="U6" s="6" t="n">
-        <v>0.7255360467141013</v>
+        <v>0.003082180784362822</v>
       </c>
       <c r="V6" s="6" t="n">
-        <v>0.6763159772921959</v>
+        <v>0</v>
       </c>
       <c r="W6" s="6" t="n">
-        <v>0.7800889879880161</v>
+        <v>0.01550981901009978</v>
       </c>
     </row>
     <row r="7">
@@ -6014,213 +6014,213 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>3</v>
+        <v>107</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>3977</v>
+        <v>59505</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>681</v>
+        <v>48650</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>10755</v>
+        <v>72796</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.01676633455893484</v>
+        <v>0.2508569938228119</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.002869512112901969</v>
+        <v>0.2050947910394133</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.04533850927342752</v>
+        <v>0.3068903472221315</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>2</v>
+        <v>82</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>1256</v>
+        <v>47755</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>0</v>
+        <v>39011</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>4884</v>
+        <v>57919</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.006810049038503074</v>
+        <v>0.2589561811206927</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0</v>
+        <v>0.2115418037555402</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.02648245407468379</v>
+        <v>0.3140745646228234</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>5</v>
+        <v>189</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>5233</v>
+        <v>107260</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>1650</v>
+        <v>91772</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>13469</v>
+        <v>121796</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.01241153686873044</v>
+        <v>0.2543995119702639</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.003914221338513997</v>
+        <v>0.217665404582844</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.0319459455427692</v>
+        <v>0.2888757864422485</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>107</v>
+        <v>233</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>59505</v>
+        <v>173724</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>48650</v>
+        <v>160050</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>72796</v>
+        <v>185721</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.2508569938228119</v>
+        <v>0.7323766716182534</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.2050947910394133</v>
+        <v>0.6747292409304828</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.3068903472221315</v>
+        <v>0.7829519197546294</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>82</v>
+        <v>196</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>47755</v>
+        <v>135402</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>39011</v>
+        <v>125204</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>57919</v>
+        <v>144135</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.2589561811206927</v>
+        <v>0.7342337698408042</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.2115418037555402</v>
+        <v>0.6789339842655926</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.3140745646228234</v>
+        <v>0.7815886031483571</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>189</v>
+        <v>429</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>107260</v>
+        <v>309126</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>91772</v>
+        <v>293710</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>121796</v>
+        <v>323151</v>
       </c>
       <c r="U9" s="6" t="n">
-        <v>0.2543995119702639</v>
+        <v>0.7331889511610056</v>
       </c>
       <c r="V9" s="6" t="n">
-        <v>0.217665404582844</v>
+        <v>0.6966246909767596</v>
       </c>
       <c r="W9" s="6" t="n">
-        <v>0.2888757864422485</v>
+        <v>0.7664532660305998</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>233</v>
+        <v>3</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>173724</v>
+        <v>3977</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>160050</v>
+        <v>681</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>185721</v>
+        <v>10755</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.7323766716182534</v>
+        <v>0.01676633455893484</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.6747292409304828</v>
+        <v>0.002869512112901969</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.7829519197546294</v>
+        <v>0.04533850927342752</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>196</v>
+        <v>2</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>135402</v>
+        <v>1256</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>125204</v>
+        <v>0</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>144135</v>
+        <v>4884</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.7342337698408042</v>
+        <v>0.006810049038503074</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.6789339842655926</v>
+        <v>0</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.7815886031483571</v>
+        <v>0.02648245407468379</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>429</v>
+        <v>5</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>309126</v>
+        <v>5233</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>293710</v>
+        <v>1650</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>323151</v>
+        <v>13469</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.7331889511610056</v>
+        <v>0.01241153686873044</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.6966246909767596</v>
+        <v>0.003914221338513997</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.7664532660305998</v>
+        <v>0.0319459455427692</v>
       </c>
     </row>
     <row r="11">
@@ -6302,213 +6302,213 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>2</v>
+        <v>79</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>722</v>
+        <v>54752</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0</v>
+        <v>42679</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>2506</v>
+        <v>66898</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.004297854003559694</v>
+        <v>0.325825376141369</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0</v>
+        <v>0.2539810224562302</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.01491214149396876</v>
+        <v>0.398102459642583</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>6579</v>
+        <v>36688</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>2955</v>
+        <v>28812</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>13453</v>
+        <v>46746</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.04259736657220257</v>
+        <v>0.23756024526065</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.01913158733673663</v>
+        <v>0.1865658697934031</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.08711002768928497</v>
+        <v>0.302689961244076</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>7301</v>
+        <v>91440</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>3509</v>
+        <v>78182</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>12842</v>
+        <v>108658</v>
       </c>
       <c r="U12" s="6" t="n">
-        <v>0.02263960678079282</v>
+        <v>0.2835549371491571</v>
       </c>
       <c r="V12" s="6" t="n">
-        <v>0.0108829072204556</v>
+        <v>0.2424420092917201</v>
       </c>
       <c r="W12" s="6" t="n">
-        <v>0.0398217392683998</v>
+        <v>0.3369459933425278</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>79</v>
+        <v>143</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>54752</v>
+        <v>112567</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>42679</v>
+        <v>100332</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>66898</v>
+        <v>124312</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.325825376141369</v>
+        <v>0.6698767698550713</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.2539810224562302</v>
+        <v>0.5970641899402709</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.398102459642583</v>
+        <v>0.7397689095559937</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>62</v>
+        <v>153</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>36688</v>
+        <v>111170</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>28812</v>
+        <v>101534</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>46746</v>
+        <v>119308</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.23756024526065</v>
+        <v>0.7198423881671473</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.1865658697934031</v>
+        <v>0.6574473456175921</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.302689961244076</v>
+        <v>0.7725372057647029</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>141</v>
+        <v>296</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>91440</v>
+        <v>223737</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>78182</v>
+        <v>205806</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>108658</v>
+        <v>237345</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.2835549371491571</v>
+        <v>0.6938054560700502</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.2424420092917201</v>
+        <v>0.6382008411191035</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.3369459933425278</v>
+        <v>0.7360043951652109</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>143</v>
+        <v>2</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>112567</v>
+        <v>722</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>100332</v>
+        <v>0</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>124312</v>
+        <v>2506</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.6698767698550713</v>
+        <v>0.004297854003559694</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.5970641899402709</v>
+        <v>0</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.7397689095559937</v>
+        <v>0.01491214149396876</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>153</v>
+        <v>8</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>111170</v>
+        <v>6579</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>101534</v>
+        <v>2955</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>119308</v>
+        <v>13453</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.7198423881671473</v>
+        <v>0.04259736657220257</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.6574473456175921</v>
+        <v>0.01913158733673663</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.7725372057647029</v>
+        <v>0.08711002768928497</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>296</v>
+        <v>10</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>223737</v>
+        <v>7301</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>205806</v>
+        <v>3509</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>237345</v>
+        <v>12842</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.6938054560700502</v>
+        <v>0.02263960678079282</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.6382008411191035</v>
+        <v>0.0108829072204556</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.7360043951652109</v>
+        <v>0.0398217392683998</v>
       </c>
     </row>
     <row r="15">
@@ -6590,213 +6590,213 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>3</v>
+        <v>71</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>2793</v>
+        <v>47072</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>852</v>
+        <v>37626</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>7819</v>
+        <v>58722</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.01648771878457812</v>
+        <v>0.2779164218295169</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.005029463738651271</v>
+        <v>0.2221418734036856</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.04616615298549916</v>
+        <v>0.3466936635870734</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>1</v>
+        <v>87</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>578</v>
+        <v>55002</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>0</v>
+        <v>44778</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>2937</v>
+        <v>64862</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.003497403216509993</v>
+        <v>0.3329601480939295</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0</v>
+        <v>0.2710678006074141</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.01777922334475089</v>
+        <v>0.3926462535348814</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>4</v>
+        <v>158</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>3370</v>
+        <v>102074</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>955</v>
+        <v>88635</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>8735</v>
+        <v>116052</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.01007381261477221</v>
+        <v>0.3050939983592399</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.002855364035541093</v>
+        <v>0.264923915191919</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.02610837320606594</v>
+        <v>0.3468725165821883</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>71</v>
+        <v>164</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>47072</v>
+        <v>119511</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>37626</v>
+        <v>108459</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>58722</v>
+        <v>129431</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.2779164218295169</v>
+        <v>0.7055958593859049</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.2221418734036856</v>
+        <v>0.6403427806222175</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.3466936635870734</v>
+        <v>0.7641609429193419</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>87</v>
+        <v>150</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>55002</v>
+        <v>109611</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>44778</v>
+        <v>99551</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>64862</v>
+        <v>119865</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.3329601480939295</v>
+        <v>0.6635424486895605</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.2710678006074141</v>
+        <v>0.6026439435156117</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.3926462535348814</v>
+        <v>0.7256170341041355</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>158</v>
+        <v>314</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>102074</v>
+        <v>229122</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>88635</v>
+        <v>214723</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>116052</v>
+        <v>242758</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.3050939983592399</v>
+        <v>0.684832189025988</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.264923915191919</v>
+        <v>0.6417940346776879</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.3468725165821883</v>
+        <v>0.7255887965970566</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>164</v>
+        <v>3</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>119511</v>
+        <v>2793</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>108459</v>
+        <v>852</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>129431</v>
+        <v>7819</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.7055958593859049</v>
+        <v>0.01648771878457812</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.6403427806222175</v>
+        <v>0.005029463738651271</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.7641609429193419</v>
+        <v>0.04616615298549916</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>150</v>
+        <v>1</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>109611</v>
+        <v>578</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>99551</v>
+        <v>0</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>119865</v>
+        <v>2937</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.6635424486895605</v>
+        <v>0.003497403216509993</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.6026439435156117</v>
+        <v>0</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.7256170341041355</v>
+        <v>0.01777922334475089</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>314</v>
+        <v>4</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>229122</v>
+        <v>3370</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>214723</v>
+        <v>955</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>242758</v>
+        <v>8735</v>
       </c>
       <c r="U18" s="6" t="n">
-        <v>0.684832189025988</v>
+        <v>0.01007381261477221</v>
       </c>
       <c r="V18" s="6" t="n">
-        <v>0.6417940346776879</v>
+        <v>0.002855364035541093</v>
       </c>
       <c r="W18" s="6" t="n">
-        <v>0.7255887965970566</v>
+        <v>0.02610837320606594</v>
       </c>
     </row>
     <row r="19">
@@ -6878,213 +6878,213 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>8</v>
+        <v>315</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>7492</v>
+        <v>195402</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>3359</v>
+        <v>173560</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>16163</v>
+        <v>217575</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.01071921357550712</v>
+        <v>0.2795744929608477</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.004805967813107631</v>
+        <v>0.2483245280293698</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.02312589527033307</v>
+        <v>0.3112999254701128</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>12</v>
+        <v>292</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>9163</v>
+        <v>171496</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>4792</v>
+        <v>154387</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>16437</v>
+        <v>189792</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.01469883667186344</v>
+        <v>0.2751008726237343</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.007686591910131019</v>
+        <v>0.2476567729280766</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.02636742748933856</v>
+        <v>0.3044497344707969</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>20</v>
+        <v>607</v>
       </c>
       <c r="R20" s="5" t="n">
-        <v>16655</v>
+        <v>366897</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>10375</v>
+        <v>339486</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>27016</v>
+        <v>399201</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>0.01259536398536086</v>
+        <v>0.2774654528769538</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>0.007845832296568182</v>
+        <v>0.2567355397286693</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>0.02043085630890165</v>
+        <v>0.3018949639309458</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>315</v>
+        <v>652</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>195402</v>
+        <v>496031</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>173560</v>
+        <v>473783</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>217575</v>
+        <v>518880</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.2795744929608477</v>
+        <v>0.7097062934636452</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.2483245280293698</v>
+        <v>0.6778740019407858</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.3112999254701128</v>
+        <v>0.7423967959422112</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>292</v>
+        <v>630</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>171496</v>
+        <v>442733</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>154387</v>
+        <v>424474</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>189792</v>
+        <v>460390</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.2751008726237343</v>
+        <v>0.7102002907044023</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.2476567729280766</v>
+        <v>0.6809106637646439</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.3044497344707969</v>
+        <v>0.7385235010908741</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>607</v>
+        <v>1282</v>
       </c>
       <c r="R21" s="5" t="n">
-        <v>366897</v>
+        <v>938765</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>339486</v>
+        <v>904712</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>399201</v>
+        <v>966284</v>
       </c>
       <c r="U21" s="6" t="n">
-        <v>0.2774654528769538</v>
+        <v>0.7099391831376854</v>
       </c>
       <c r="V21" s="6" t="n">
-        <v>0.2567355397286693</v>
+        <v>0.6841866096325415</v>
       </c>
       <c r="W21" s="6" t="n">
-        <v>0.3018949639309458</v>
+        <v>0.7307505790130875</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>652</v>
+        <v>8</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>496031</v>
+        <v>7492</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>473783</v>
+        <v>3359</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>518880</v>
+        <v>16163</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.7097062934636452</v>
+        <v>0.01071921357550712</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.6778740019407858</v>
+        <v>0.004805967813107631</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.7423967959422112</v>
+        <v>0.02312589527033307</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>630</v>
+        <v>12</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>442733</v>
+        <v>9163</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>424474</v>
+        <v>4792</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>460390</v>
+        <v>16437</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.7102002907044023</v>
+        <v>0.01469883667186344</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.6809106637646439</v>
+        <v>0.007686591910131019</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.7385235010908741</v>
+        <v>0.02636742748933856</v>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>1282</v>
+        <v>20</v>
       </c>
       <c r="R22" s="5" t="n">
-        <v>938765</v>
+        <v>16655</v>
       </c>
       <c r="S22" s="5" t="n">
-        <v>904712</v>
+        <v>10375</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>966284</v>
+        <v>27016</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>0.7099391831376854</v>
+        <v>0.01259536398536086</v>
       </c>
       <c r="V22" s="6" t="n">
-        <v>0.6841866096325415</v>
+        <v>0.007845832296568182</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>0.7307505790130875</v>
+        <v>0.02043085630890165</v>
       </c>
     </row>
     <row r="23">
